--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\geola\Documents\02_ACADEMIC\FYP\soc_rag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69657A1E-B171-423F-B1DA-74D350E3D754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57ED0AD8-24FC-481C-9200-C0F06DF9489E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="143">
   <si>
     <t>2025-03-07T11:37:22.109Z server52 DatabaseConnector [INFO]: Operation started for user 520</t>
   </si>
@@ -448,6 +448,12 @@
   </si>
   <si>
     <t>(?P&lt;date&gt;\d{4}-\d{2}-\d{2})\s(?P&lt;time&gt;\d{2}:\d{2}:\d{2},\d+)\s(?P&lt;severity&gt;[A-Z]+)\s\[(?P&lt;thread&gt;.+?)\]\s(?P&lt;class&gt;[\w\.]+):\s(?P&lt;message&gt;.+)</t>
+  </si>
+  <si>
+    <t>.+?&lt;(?P&lt;process&gt;[^:]+):(?P&lt;level&gt;\w+)&gt;\s+\d\s+(?P&lt;timestamp&gt;[\d\-T:+\.]+)\s+(?P&lt;hostname&gt;\S+)\s+\S+[\-\s]+(?P&lt;log_format&gt;LEEF:2.0|CEF:0)\|radiflow\|isid\|(?P&lt;version&gt;[^\|]+)\|(?P&lt;vmid&gt;\d+)\|(?P&lt;threatname&gt;[^\|]+)\|(?P&lt;severity&gt;\w+)\|cat='(?P&lt;category&gt;\w+)'\s*id=(?P&lt;id&gt;\d+)\s*src=(?P&lt;src_ip&gt;\d+\.\d+\.\d+\.\d+)\s*dst=(?P&lt;dst_ip&gt;\d+\.\d+\.\d+\.\d+)\s*pt=(?P&lt;pt&gt;\d+)\s*PtName=(?P&lt;ptname&gt;\S+)\s*SrcName=(?P&lt;srcname&gt;\S+)\s*DstName=(?P&lt;dstname&gt;\S+)\s*SrcMac=(?P&lt;srcmac&gt;\S+)\s*DstMac=(?P&lt;dstmac&gt;\S+)\s*SrcVendor=(?P&lt;srcvendor&gt;.+?)\s+DstVendor=(?P&lt;dstvendor&gt;.+?)\s+SrcType=(?P&lt;srctype&gt;\S+)\s*DstType=(?P&lt;dsttype&gt;\S+).*$</t>
+  </si>
+  <si>
+    <t>^(?P&lt;timestamp&gt;\d{2}\/\d{2}\/\d{2} \d{2}:\d{2}:\d{2})\s+(?P&lt;log_level&gt;[A-Z]+)\s+(?P&lt;module&gt;[\w\.]+):\s+(?P&lt;message&gt;.+)</t>
   </si>
 </sst>
 </file>
@@ -767,6 +773,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="21.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -800,6 +809,9 @@
       <c r="B3" t="s">
         <v>1</v>
       </c>
+      <c r="C3" t="s">
+        <v>141</v>
+      </c>
       <c r="E3" t="s">
         <v>100</v>
       </c>
@@ -811,6 +823,9 @@
       <c r="B4" t="s">
         <v>2</v>
       </c>
+      <c r="C4" t="s">
+        <v>142</v>
+      </c>
       <c r="E4" t="s">
         <v>101</v>
       </c>
@@ -1875,5 +1890,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>